--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/PENNSYLVANIA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/PENNSYLVANIA_2022.xlsx
@@ -1903,7 +1903,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="87">
@@ -3217,7 +3217,7 @@
         <v>48</v>
       </c>
       <c r="D159">
-        <v>0.009609609609609609</v>
+        <v>0.009609609609609607</v>
       </c>
     </row>
     <row r="160">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C173">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C179">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C480">
@@ -10327,7 +10327,7 @@
         <v>45</v>
       </c>
       <c r="D554">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="555">
